--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136759776</v>
+        <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>98215</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skultuna, Vstm</t>
+          <t>Porsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574739</v>
+        <v>574868</v>
       </c>
       <c r="R2" t="n">
-        <v>6618994</v>
+        <v>6618932</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,24 +786,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759776</t>
+          <t>https://artportalen.se/Sighting/136986033</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136759777</v>
+        <v>136759776</v>
       </c>
       <c r="B3" t="n">
         <v>98215</v>
@@ -840,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574652</v>
+        <v>574739</v>
       </c>
       <c r="R3" t="n">
-        <v>6618966</v>
+        <v>6618994</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,6 +917,127 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136759776</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136759777</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skultuna, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>574652</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6618966</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136759777</t>
         </is>
@@ -924,6 +1047,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92509</v>
+        <v>92511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>136759776</v>
       </c>
       <c r="B3" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136759777</v>
       </c>
       <c r="B4" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92511</v>
+        <v>92513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>136759776</v>
       </c>
       <c r="B3" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136759777</v>
       </c>
       <c r="B4" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92513</v>
+        <v>92514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>136759776</v>
       </c>
       <c r="B3" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136759777</v>
       </c>
       <c r="B4" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92514</v>
+        <v>92520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>136759776</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136759777</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>136759776</v>
       </c>
       <c r="B3" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136759777</v>
       </c>
       <c r="B4" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>136759776</v>
       </c>
       <c r="B3" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136759777</v>
       </c>
       <c r="B4" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>136759776</v>
       </c>
       <c r="B3" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136759777</v>
       </c>
       <c r="B4" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92526</v>
+        <v>92539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>136759776</v>
       </c>
       <c r="B3" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136759777</v>
       </c>
       <c r="B4" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>136759776</v>
       </c>
       <c r="B3" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136759777</v>
       </c>
       <c r="B4" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92541</v>
+        <v>92544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>136759776</v>
       </c>
       <c r="B3" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136759777</v>
       </c>
       <c r="B4" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92544</v>
+        <v>92554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,49 +803,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136759776</v>
+        <v>137097998</v>
       </c>
       <c r="B3" t="n">
-        <v>98256</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skultuna, Vstm</t>
+          <t>Porsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574739</v>
+        <v>574601</v>
       </c>
       <c r="R3" t="n">
-        <v>6618994</v>
+        <v>6618975</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,27 +877,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,31 +903,36 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759776</t>
+          <t>https://artportalen.se/Sighting/137097998</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136759777</v>
+        <v>136759776</v>
       </c>
       <c r="B4" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574652</v>
+        <v>574739</v>
       </c>
       <c r="R4" t="n">
-        <v>6618966</v>
+        <v>6618994</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1039,7 +1044,254 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136759776</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136759777</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98266</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skultuna, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>574652</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6618966</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136759777</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137099376</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98266</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Porsmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>574657</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6619000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Häll- och blockskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137099376</t>
         </is>
       </c>
     </row>
@@ -1048,6 +1300,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92554</v>
+        <v>92555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>137097998</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>136759776</v>
       </c>
       <c r="B4" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136759777</v>
       </c>
       <c r="B5" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>137099376</v>
       </c>
       <c r="B6" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92555</v>
+        <v>92558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>137097998</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>137099376</v>
       </c>
       <c r="B6" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>137097998</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>137099376</v>
       </c>
       <c r="B6" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>137097998</v>
       </c>
       <c r="B3" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>137099376</v>
       </c>
       <c r="B6" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>137097998</v>
       </c>
       <c r="B3" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>137099376</v>
       </c>
       <c r="B6" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>137097998</v>
       </c>
       <c r="B3" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>137099376</v>
       </c>
       <c r="B6" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>137097998</v>
       </c>
       <c r="B3" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>137099376</v>
       </c>
       <c r="B6" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92581</v>
+        <v>92582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39917-2026 artfynd.xlsx
+++ b/artfynd/A 39917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986033</v>
       </c>
       <c r="B2" t="n">
-        <v>92582</v>
+        <v>92585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>137097998</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>137099376</v>
       </c>
       <c r="B6" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
